--- a/ShooterParams.xlsx
+++ b/ShooterParams.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\StudioProjects\FTC_25-26_34063\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2795A5AA-4C64-40CE-BC54-E81FEB50EAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF6BBEE0-0F3C-4E90-BEF7-71898B7E43F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="23.01.2026" sheetId="1" r:id="rId1"/>
@@ -408,12 +408,6 @@
       <c r="A9">
         <v>0.75</v>
       </c>
-      <c r="B9">
-        <v>0.42499999999999999</v>
-      </c>
-      <c r="C9">
-        <v>2500</v>
-      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
@@ -425,31 +419,43 @@
         <v>0.9</v>
       </c>
       <c r="B11">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="C11">
-        <v>2750</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1</v>
       </c>
+      <c r="B12">
+        <v>0.1</v>
+      </c>
+      <c r="C12">
+        <v>2800</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1.1000000000000001</v>
       </c>
+      <c r="B13">
+        <v>0.1</v>
+      </c>
+      <c r="C13">
+        <v>2800</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1.2</v>
       </c>
       <c r="B14">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="C14">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -457,10 +463,10 @@
         <v>1.3</v>
       </c>
       <c r="B15">
-        <v>0.67500000000000004</v>
+        <v>0.2</v>
       </c>
       <c r="C15">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -468,10 +474,10 @@
         <v>1.4</v>
       </c>
       <c r="B16">
-        <v>0.72499999999999998</v>
+        <v>0.25</v>
       </c>
       <c r="C16">
-        <v>3000</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -479,7 +485,7 @@
         <v>1.5</v>
       </c>
       <c r="B17">
-        <v>0.75</v>
+        <v>0.35</v>
       </c>
       <c r="C17">
         <v>3000</v>
@@ -490,7 +496,7 @@
         <v>1.6</v>
       </c>
       <c r="B18">
-        <v>0.75</v>
+        <v>0.35</v>
       </c>
       <c r="C18">
         <v>3000</v>
@@ -501,10 +507,10 @@
         <v>1.7</v>
       </c>
       <c r="B19">
-        <v>0.77500000000000002</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="C19">
-        <v>3000</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -512,7 +518,7 @@
         <v>1.8</v>
       </c>
       <c r="B20">
-        <v>0.77500000000000002</v>
+        <v>0.45</v>
       </c>
       <c r="C20">
         <v>3100</v>
@@ -523,10 +529,10 @@
         <v>1.9</v>
       </c>
       <c r="B21">
-        <v>0.77500000000000002</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="C21">
-        <v>3150</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -534,10 +540,10 @@
         <v>2</v>
       </c>
       <c r="B22">
-        <v>0.77500000000000002</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="C22">
-        <v>3250</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
@@ -545,10 +551,10 @@
         <v>2.1</v>
       </c>
       <c r="B23">
-        <v>0.8</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="C23">
-        <v>3250</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -556,10 +562,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B24">
-        <v>0.8</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="C24">
-        <v>3250</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -567,10 +573,10 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="B25">
-        <v>0.82499999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="C25">
-        <v>3300</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -578,10 +584,10 @@
         <v>2.4</v>
       </c>
       <c r="B26">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="C26">
-        <v>3350</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
@@ -589,7 +595,7 @@
         <v>2.5</v>
       </c>
       <c r="B27">
-        <v>0.85</v>
+        <v>0.65</v>
       </c>
       <c r="C27">
         <v>3500</v>
@@ -600,7 +606,7 @@
         <v>2.6</v>
       </c>
       <c r="B28">
-        <v>0.85</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="C28">
         <v>3500</v>
@@ -611,10 +617,10 @@
         <v>2.7</v>
       </c>
       <c r="B29">
-        <v>0.85</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="C29">
-        <v>3500</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
@@ -667,10 +673,10 @@
         <v>3.7</v>
       </c>
       <c r="B39">
-        <v>0.875</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="C39">
-        <v>4000</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
